--- a/r5-aist-trustworthyai-main/all-profiles.xlsx
+++ b/r5-aist-trustworthyai-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:13:25+00:00</t>
+    <t>2026-10-02T06:10:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1384,10 +1384,10 @@
     <t>euDatabaseId</t>
   </si>
   <si>
-    <t>Trust AI database registration number</t>
-  </si>
-  <si>
-    <t>The unique registration number assigned to the high-risk AI system in the official Trust AI database.</t>
+    <t>EU database registration number</t>
+  </si>
+  <si>
+    <t>The unique registration number assigned to the high-risk AI system in the official EU database (AI Act Art. 49).</t>
   </si>
   <si>
     <t>AI Act Art. 49 | EU Database Registration</t>
@@ -3830,7 +3830,7 @@
     <t>Trust_AIModelCard</t>
   </si>
   <si>
-    <t>Trust AI Act Model Card</t>
+    <t>Trust AI Model Card</t>
   </si>
   <si>
     <t>A DocumentReference profile representing technical documentation about an AI system, such as intended use, limitations, risk-related information, performance-related information, and model documentation.</t>
@@ -6123,7 +6123,7 @@
     <t>Trust AI Patient Explanation Communication</t>
   </si>
   <si>
-    <t>A Communication profile documenting that an explanation regarding an AI-supported clinical decision was provided to a patient. The explanation may describe the role of the AI system, the related human oversight, and the key elements of the resulting clinical decision in accordance with Article 86 of the Trust AI Act.</t>
+    <t>A Communication profile documenting that an explanation regarding an AI-supported clinical decision was provided to a patient. The explanation may describe the role of the AI system, the related human oversight, and the key elements of the resulting clinical decision in accordance with Article 86 of the EU AI Act.</t>
   </si>
   <si>
     <t>Communication</t>
